--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1301-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1301-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAE564EC-5C9F-4FF6-8CFD-B48EAEDA64C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DCC4C35-251F-451F-836A-3BAF4E4E4A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{B0FFF607-8AE0-47F8-BFB4-BF92BA526AC4}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{5733DDBD-0192-46A4-AA5E-645F13165919}"/>
   </bookViews>
   <sheets>
     <sheet name="1301-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1622,27 +1622,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C960BF-032E-435C-B9DB-5D12C5309E9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09BA348D-6678-48C4-86B1-A13EBA648F69}">
   <dimension ref="A1:X59"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1676,7 +1675,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1712,7 +1711,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1764,7 +1763,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1832,7 +1831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1904,7 +1903,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1976,7 +1975,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2048,7 +2047,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2120,7 +2119,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2192,7 +2191,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2336,7 +2335,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2408,7 +2407,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2480,7 +2479,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2552,7 +2551,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2624,7 +2623,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2696,7 +2695,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2768,7 +2767,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2840,7 +2839,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2912,7 +2911,7 @@
         <v>8.9499999999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2984,7 +2983,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3056,7 +3055,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3128,7 +3127,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3200,7 +3199,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3272,7 +3271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3344,7 +3343,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3416,7 +3415,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2002</v>
       </c>
@@ -3488,7 +3487,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="18" t="s">
@@ -3516,7 +3515,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2001</v>
       </c>
@@ -3588,7 +3587,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="53"/>
       <c r="B30" s="54"/>
       <c r="C30" s="20" t="s">
@@ -3616,7 +3615,7 @@
       <c r="W30" s="60"/>
       <c r="X30" s="56"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>2000</v>
       </c>
@@ -3688,7 +3687,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="43"/>
       <c r="B32" s="44"/>
       <c r="C32" s="18" t="s">
@@ -3716,7 +3715,7 @@
       <c r="W32" s="50"/>
       <c r="X32" s="46"/>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1999</v>
       </c>
@@ -3788,7 +3787,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>1998</v>
       </c>
@@ -3860,7 +3859,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="43"/>
       <c r="B35" s="44"/>
       <c r="C35" s="18" t="s">
@@ -3888,7 +3887,7 @@
       <c r="W35" s="50"/>
       <c r="X35" s="46"/>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1997</v>
       </c>
@@ -3960,7 +3959,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>1996</v>
       </c>
@@ -4032,7 +4031,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="43"/>
       <c r="B38" s="44"/>
       <c r="C38" s="18" t="s">
@@ -4060,7 +4059,7 @@
       <c r="W38" s="50"/>
       <c r="X38" s="46"/>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="51">
         <v>1995</v>
       </c>
@@ -4132,7 +4131,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="53"/>
       <c r="B40" s="54"/>
       <c r="C40" s="20" t="s">
@@ -4160,7 +4159,7 @@
       <c r="W40" s="60"/>
       <c r="X40" s="56"/>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="41">
         <v>1994</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="43"/>
       <c r="B42" s="44"/>
       <c r="C42" s="18" t="s">
@@ -4260,7 +4259,7 @@
       <c r="W42" s="50"/>
       <c r="X42" s="46"/>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="51">
         <v>1993</v>
       </c>
@@ -4332,7 +4331,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="53"/>
       <c r="B44" s="54"/>
       <c r="C44" s="20" t="s">
@@ -4360,7 +4359,7 @@
       <c r="W44" s="60"/>
       <c r="X44" s="56"/>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="41">
         <v>1992</v>
       </c>
@@ -4432,7 +4431,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="43"/>
       <c r="B46" s="44"/>
       <c r="C46" s="18" t="s">
@@ -4460,7 +4459,7 @@
       <c r="W46" s="50"/>
       <c r="X46" s="46"/>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="51">
         <v>1991</v>
       </c>
@@ -4532,7 +4531,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="53"/>
       <c r="B48" s="54"/>
       <c r="C48" s="20" t="s">
@@ -4560,7 +4559,7 @@
       <c r="W48" s="60"/>
       <c r="X48" s="56"/>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="41">
         <v>1990</v>
       </c>
@@ -4632,7 +4631,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="43"/>
       <c r="B50" s="44"/>
       <c r="C50" s="18" t="s">
@@ -4660,7 +4659,7 @@
       <c r="W50" s="50"/>
       <c r="X50" s="46"/>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="51">
         <v>1989</v>
       </c>
@@ -4732,7 +4731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="53"/>
       <c r="B52" s="54"/>
       <c r="C52" s="20" t="s">
@@ -4760,7 +4759,7 @@
       <c r="W52" s="60"/>
       <c r="X52" s="56"/>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>1988</v>
       </c>
@@ -4832,7 +4831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="39">
         <v>1987</v>
       </c>
@@ -4904,7 +4903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="37">
         <v>1986</v>
       </c>
@@ -4976,7 +4975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="39">
         <v>1985</v>
       </c>
@@ -5048,7 +5047,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="37">
         <v>1984</v>
       </c>
@@ -5120,7 +5119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="39">
         <v>1983</v>
       </c>
@@ -5192,7 +5191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="37" t="s">
         <v>76</v>
       </c>
